--- a/IEEE TIM data/HUMAN LAB VALIDATION/Results/Duration_Correlation_BlandAltman/Duration_Correlation_BlandAltman.xlsx
+++ b/IEEE TIM data/HUMAN LAB VALIDATION/Results/Duration_Correlation_BlandAltman/Duration_Correlation_BlandAltman.xlsx
@@ -628,7 +628,7 @@
         <v>3.64</v>
       </c>
       <c r="E6">
-        <v>2.691</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -781,7 +781,7 @@
         <v>1.636</v>
       </c>
       <c r="E15">
-        <v>1.299</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -900,7 +900,7 @@
         <v>2.66</v>
       </c>
       <c r="E22">
-        <v>2.419</v>
+        <v>2.475</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -917,7 +917,7 @@
         <v>4.833</v>
       </c>
       <c r="E23">
-        <v>2.793</v>
+        <v>3.802</v>
       </c>
     </row>
   </sheetData>
@@ -1006,40 +1006,40 @@
         <v>2.944</v>
       </c>
       <c r="G2">
-        <v>2.046</v>
+        <v>2.1023</v>
       </c>
       <c r="H2">
-        <v>0.5852000000000001</v>
+        <v>0.6856</v>
       </c>
       <c r="I2">
-        <v>1.7865</v>
+        <v>1.7983</v>
       </c>
       <c r="J2">
-        <v>2.3055</v>
+        <v>2.4063</v>
       </c>
       <c r="K2">
-        <v>0.869</v>
+        <v>0.9431</v>
       </c>
       <c r="L2">
-        <v>1.546829465924179E-07</v>
+        <v>5.05102328762307E-11</v>
       </c>
       <c r="M2">
-        <v>0.5279</v>
+        <v>0.4716</v>
       </c>
       <c r="N2">
-        <v>0.1934</v>
+        <v>0.131</v>
       </c>
       <c r="O2">
-        <v>-0.327</v>
+        <v>-0.1076</v>
       </c>
       <c r="P2">
-        <v>1.3829</v>
+        <v>1.0509</v>
       </c>
       <c r="Q2">
-        <v>0.5911999999999999</v>
+        <v>0.5119</v>
       </c>
       <c r="R2">
-        <v>0.0038</v>
+        <v>0.0149</v>
       </c>
     </row>
   </sheetData>

--- a/IEEE TIM data/HUMAN LAB VALIDATION/Results/Duration_Correlation_BlandAltman/Duration_Correlation_BlandAltman.xlsx
+++ b/IEEE TIM data/HUMAN LAB VALIDATION/Results/Duration_Correlation_BlandAltman/Duration_Correlation_BlandAltman.xlsx
@@ -165,7 +165,7 @@
     <t>Computed fresh from Script1_0.4sec_threshold_performance_metrics.py (imported unmodified), not from any pre-existing summary spreadsheet.</t>
   </si>
   <si>
-    <t>Camera/FRIENDS mean duration 95% CI: t-interval across the 22 participant-level means (mean +/- t(0.975, n-1) * SD/sqrt(n)) -- the same t-interval method used for the pooled individual-puff duration distribution in Script2.</t>
+    <t>Camera/FRIENDS mean duration 95% CI: t-interval across the 22 participant-level means (mean +/- t(0.975, n-1) * SD/sqrt(n)) -- the same t-interval method used for the pooled individual-puff duration distribution in Script5.</t>
   </si>
   <si>
     <t>Bland-Altman: bias = mean(Camera-FRIENDS); LoA = bias +/- 1.96*SD(diff); proportional bias = Pearson r between per-participant mean and difference.</t>

--- a/IEEE TIM data/HUMAN LAB VALIDATION/Results/Duration_Correlation_BlandAltman/Duration_Correlation_BlandAltman.xlsx
+++ b/IEEE TIM data/HUMAN LAB VALIDATION/Results/Duration_Correlation_BlandAltman/Duration_Correlation_BlandAltman.xlsx
@@ -1,206 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Per_Participant_Durations" sheetId="1" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" r:id="rId2"/>
-    <sheet name="Method" sheetId="3" r:id="rId3"/>
+    <sheet name="Per_Participant_Durations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Method" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
-  <si>
-    <t>Participant</t>
-  </si>
-  <si>
-    <t>Camera Avg Puff Duration</t>
-  </si>
-  <si>
-    <t>FRIENDS Avg Puff Duration</t>
-  </si>
-  <si>
-    <t>Avg Hit Duration (Camera)</t>
-  </si>
-  <si>
-    <t>Avg Hit Duration (FRIENDS)</t>
-  </si>
-  <si>
-    <t>FRIENDS2076</t>
-  </si>
-  <si>
-    <t>FRIENDS2080</t>
-  </si>
-  <si>
-    <t>FRIENDS2081</t>
-  </si>
-  <si>
-    <t>FRIENDS2091</t>
-  </si>
-  <si>
-    <t>FRIENDS2094</t>
-  </si>
-  <si>
-    <t>FRIENDS2112</t>
-  </si>
-  <si>
-    <t>FRIENDS2136</t>
-  </si>
-  <si>
-    <t>FRIENDS2137</t>
-  </si>
-  <si>
-    <t>FRIENDS2138</t>
-  </si>
-  <si>
-    <t>FRIENDS2150</t>
-  </si>
-  <si>
-    <t>FRIENDS2160</t>
-  </si>
-  <si>
-    <t>FRIENDS2164</t>
-  </si>
-  <si>
-    <t>FRIENDS2173</t>
-  </si>
-  <si>
-    <t>FRIENDS2191</t>
-  </si>
-  <si>
-    <t>FRIENDS2192</t>
-  </si>
-  <si>
-    <t>FRIENDS2202</t>
-  </si>
-  <si>
-    <t>FRIENDS2203</t>
-  </si>
-  <si>
-    <t>FRIENDS2209</t>
-  </si>
-  <si>
-    <t>FRIENDS2219</t>
-  </si>
-  <si>
-    <t>FRIENDS2221</t>
-  </si>
-  <si>
-    <t>FRIENDS2226</t>
-  </si>
-  <si>
-    <t>FRIENDS2236</t>
-  </si>
-  <si>
-    <t>Duration definition</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>Camera mean (s)</t>
-  </si>
-  <si>
-    <t>Camera SD (s)</t>
-  </si>
-  <si>
-    <t>Camera 95% CI lower (s)</t>
-  </si>
-  <si>
-    <t>Camera 95% CI upper (s)</t>
-  </si>
-  <si>
-    <t>FRIENDS mean (s)</t>
-  </si>
-  <si>
-    <t>FRIENDS SD (s)</t>
-  </si>
-  <si>
-    <t>FRIENDS 95% CI lower (s)</t>
-  </si>
-  <si>
-    <t>FRIENDS 95% CI upper (s)</t>
-  </si>
-  <si>
-    <t>Pearson r</t>
-  </si>
-  <si>
-    <t>Pearson p</t>
-  </si>
-  <si>
-    <t>BA mean bias (s)</t>
-  </si>
-  <si>
-    <t>BA bias 95% CI (+/-)</t>
-  </si>
-  <si>
-    <t>BA LoA lower (s)</t>
-  </si>
-  <si>
-    <t>BA LoA upper (s)</t>
-  </si>
-  <si>
-    <t>Proportional bias r</t>
-  </si>
-  <si>
-    <t>Proportional bias p</t>
-  </si>
-  <si>
-    <t>Hits only</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>Duration = Avg Hit Duration (Camera) vs Avg Hit Duration (FRIENDS): only puffs that were correctly matched between video and device (TP puffs). This is the only valid definition for a Bland-Altman agreement analysis, since each pair must be two measurements of the same event -- an "all puffs" comparison would mix in FRIENDS false-positive durations (no video counterpart) and camera missed-puff durations (no FRIENDS counterpart), conflating detection disagreement (already covered by the Script1 confusion matrix) with duration-measurement disagreement.</t>
-  </si>
-  <si>
-    <t>Computed fresh from Script1_0.4sec_threshold_performance_metrics.py (imported unmodified), not from any pre-existing summary spreadsheet.</t>
-  </si>
-  <si>
-    <t>Camera/FRIENDS mean duration 95% CI: t-interval across the 22 participant-level means (mean +/- t(0.975, n-1) * SD/sqrt(n)) -- the same t-interval method used for the pooled individual-puff duration distribution in Script5.</t>
-  </si>
-  <si>
-    <t>Bland-Altman: bias = mean(Camera-FRIENDS); LoA = bias +/- 1.96*SD(diff); proportional bias = Pearson r between per-participant mean and difference.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -208,36 +44,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -525,559 +410,673 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Camera Avg Puff Duration</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FRIENDS Avg Puff Duration</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Avg Hit Duration (Camera)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Avg Hit Duration (FRIENDS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FRIENDS2076</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>2.776</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>1.893</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>2.776</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>1.913</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FRIENDS2080</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>1.156</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>1.209</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>1.161</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>1.209</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FRIENDS2081</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>2.447</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>2.07</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>2.447</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>2.07</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FRIENDS2091</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>3.211</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>2.725</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>3.211</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>2.744</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FRIENDS2094</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>3.171</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>1.887</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>3.64</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>2.84</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FRIENDS2112</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>2.924</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>2.462</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>2.924</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>2.462</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FRIENDS2136</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>2.005</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>1.805</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>1.995</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>1.805</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FRIENDS2137</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>1.702</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>2.16</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>1.684</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>1.66</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FRIENDS2138</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>2.262</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>1.792</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>2.262</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>1.792</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FRIENDS2150</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>3.024</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>2.753</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>3.024</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>2.753</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FRIENDS2160</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>2.321</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>1.621</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>2.32</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>1.483</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FRIENDS2164</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>3.309</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>2.927</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>3.309</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>2.927</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FRIENDS2173</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>2.282</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>1.524</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>2.282</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>1.436</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FRIENDS2191</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>1.636</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>1.286</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>1.636</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>1.323</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FRIENDS2192</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>1.77</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>1.819</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>1.77</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>1.666</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FRIENDS2202</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>3.653</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>2.944</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>3.653</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>2.944</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FRIENDS2203</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>2.49</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>1.791</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>2.49</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>1.791</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FRIENDS2209</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>1.589</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>1.088</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>1.589</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>1.111</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FRIENDS2219</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>2.478</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>1.938</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>2.516</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>1.938</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FRIENDS2221</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>2.444</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>1.925</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>2.444</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>2.106</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FRIENDS2226</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>2.655</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>2.298</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>2.66</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>2.475</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FRIENDS2236</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>4.833</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>2.793</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>4.833</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>3.802</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Duration definition</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Camera mean (s)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Camera SD (s)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Camera 95% CI lower (s)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Camera 95% CI upper (s)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>FRIENDS mean (s)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>FRIENDS SD (s)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>FRIENDS 95% CI lower (s)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>FRIENDS 95% CI upper (s)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Pearson r</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Pearson p</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>BA mean bias (s)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>BA bias 95% CI (+/-)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>BA LoA lower (s)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>BA LoA upper (s)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Proportional bias r</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Proportional bias p</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Hits only</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>22</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>2.5739</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>0.8348</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>2.2038</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>2.944</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>2.1023</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>0.6856</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>1.7983</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>2.4063</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>0.9431</v>
       </c>
-      <c r="L2">
-        <v>5.05102328762307E-11</v>
-      </c>
-      <c r="M2">
+      <c r="L2" t="n">
+        <v>5.05102328762307e-11</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.4716</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>0.131</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>-0.1076</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>1.0509</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>0.5119</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>0.0149</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>50</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Duration = Avg Hit Duration (Camera) vs Avg Hit Duration (FRIENDS): only puffs that were correctly matched between video and device (TP puffs). This is the only valid definition for a Bland-Altman agreement analysis, since each pair must be two measurements of the same event -- an "all puffs" comparison would mix in FRIENDS false-positive durations (no video counterpart) and camera missed-puff durations (no FRIENDS counterpart), conflating detection disagreement (already covered by the Script1 confusion matrix) with duration-measurement disagreement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Computed fresh from Script1_0.4sec_threshold_performance_metrics.py (imported unmodified), not from any pre-existing summary spreadsheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Camera/FRIENDS mean duration 95% CI: t-interval across the 22 participant-level means (mean +/- t(0.975, n-1) * SD/sqrt(n)) -- the same t-interval method used for the pooled individual-puff duration distribution in Script5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bland-Altman: bias = mean(Camera-FRIENDS); LoA = bias +/- 1.96*SD(diff); proportional bias = Pearson r between per-participant mean and difference.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>